--- a/tests/fixtures/expected/touren_tr.xlsx
+++ b/tests/fixtures/expected/touren_tr.xlsx
@@ -621,7 +621,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2606KSKlettersteigtourTraversata</t>
+          <t>26 TR2026-001 Klettersteigtour Traversata</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Klettersteigtour Traversata</t>
+          <t>TR2026-001 Klettersteigtour Traversata</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -738,7 +738,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2605WANFamilienwanderungRuwertal</t>
+          <t>26 TR2026-002 Familienwanderung Ruwertal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Familienwanderung Ruwertal</t>
+          <t>TR2026-002 Familienwanderung Ruwertal</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/tests/fixtures/expected/touren_tr.xlsx
+++ b/tests/fixtures/expected/touren_tr.xlsx
@@ -704,7 +704,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>391</v>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Mitglieder: 15&lt;br /&gt;Die Kosten für Anreise, Unterkunft und Verpflegung muss jeder Teilnehmer selbst tragen. Die Teilnehmer eines außerhalb der Region stattfindenden Ausbildungskurses oder einer Ausbildungstour ermöglichen dem Kursleiter bzw. weiteren Ausbildern eine kostenfreie An- und Abreise. Einzelheiten sind mit dem Kursleiter zu klären.&lt;/p&gt;</t>

--- a/tests/fixtures/expected/touren_tr.xlsx
+++ b/tests/fixtures/expected/touren_tr.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>/264 - Sektion Trier/Gruppen/Wandergruppe</t>
+          <t>/264 - Sektion Trier/Gruppen/Bergsteigen</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/tests/fixtures/expected/touren_tr.xlsx
+++ b/tests/fixtures/expected/touren_tr.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[dates]2026-06-14 00:00:00 bis 2026-06-14 23:59:59</t>
+          <t>[dates]2026-06-14 00:00:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[dates]2026-05-24 00:00:00 bis 2026-05-24 23:59:59</t>
+          <t>[dates]2026-05-24 00:00:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
